--- a/Excel/MonsterShengxiaoConfig.xlsx
+++ b/Excel/MonsterShengxiaoConfig.xlsx
@@ -98,10 +98,10 @@
     <t>地级·</t>
   </si>
   <si>
-    <t>500000</t>
-  </si>
-  <si>
-    <t>5000000000</t>
+    <t>400000</t>
+  </si>
+  <si>
+    <t>3000000000</t>
   </si>
   <si>
     <t>30000000000</t>
@@ -110,10 +110,10 @@
     <t>玄级·</t>
   </si>
   <si>
-    <t>1500000</t>
-  </si>
-  <si>
-    <t>25000000000</t>
+    <t>800000</t>
+  </si>
+  <si>
+    <t>9000000000</t>
   </si>
   <si>
     <t>100000000000</t>
@@ -122,10 +122,10 @@
     <t>黄级·</t>
   </si>
   <si>
-    <t>4000000</t>
-  </si>
-  <si>
-    <t>80000000000</t>
+    <t>2000000</t>
+  </si>
+  <si>
+    <t>20000000000</t>
   </si>
   <si>
     <t>300000000000</t>
@@ -773,11 +773,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -794,14 +792,12 @@
     <xf numFmtId="176" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -811,9 +807,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1137,735 +1130,727 @@
   <dimension ref="A1:S29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="8" style="5" customWidth="1"/>
-    <col min="3" max="3" width="9.875" style="6" customWidth="1"/>
+    <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="8" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9.875" style="4" customWidth="1"/>
     <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="17" style="7" customWidth="1"/>
-    <col min="7" max="8" width="19.25" style="7" customWidth="1"/>
-    <col min="9" max="9" width="11.5" style="5" customWidth="1"/>
-    <col min="10" max="10" width="9.875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="10.375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="12" style="5" customWidth="1"/>
-    <col min="13" max="13" width="9.375" style="5" customWidth="1"/>
-    <col min="14" max="14" width="15.25" style="5" customWidth="1"/>
-    <col min="15" max="15" width="17.0833333333333" style="5" customWidth="1"/>
-    <col min="16" max="16" width="11.625" style="7" customWidth="1"/>
-    <col min="17" max="17" width="17" style="7" customWidth="1"/>
-    <col min="18" max="18" width="19.25" style="7" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="5"/>
+    <col min="5" max="5" width="11.625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="17" style="5" customWidth="1"/>
+    <col min="7" max="8" width="19.25" style="5" customWidth="1"/>
+    <col min="9" max="9" width="11.5" style="3" customWidth="1"/>
+    <col min="10" max="10" width="9.875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="10.375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="12" style="3" customWidth="1"/>
+    <col min="13" max="13" width="9.375" style="3" customWidth="1"/>
+    <col min="14" max="14" width="15.25" style="3" customWidth="1"/>
+    <col min="15" max="15" width="17.0833333333333" style="3" customWidth="1"/>
+    <col min="16" max="16" width="11.625" style="5" customWidth="1"/>
+    <col min="17" max="17" width="17" style="5" customWidth="1"/>
+    <col min="18" max="18" width="19.25" style="5" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A1" s="5"/>
-      <c r="B1" s="5"/>
-      <c r="C1" s="6"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="12"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="4"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="4"/>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="12"/>
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="4"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="9" t="s">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
-      <c r="S3" s="12"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="4"/>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="9" t="s">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="10" t="s">
+      <c r="N4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="O4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="12"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="4"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="9" t="s">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="L5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="10" t="s">
+      <c r="M5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="10" t="s">
+      <c r="N5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="12"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="4"/>
     </row>
     <row r="6" customHeight="1" spans="3:19">
-      <c r="C6" s="12">
+      <c r="C6" s="4">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="10">
         <v>0</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="2">
+        <v>25</v>
+      </c>
+      <c r="J6" s="2">
         <v>100</v>
       </c>
-      <c r="J6" s="3">
-        <v>100</v>
-      </c>
-      <c r="K6" s="3">
+      <c r="K6" s="2">
         <v>1800</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="2">
         <v>1800</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="2">
         <v>99</v>
       </c>
-      <c r="N6" s="20" t="s">
+      <c r="N6" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="O6" s="20" t="s">
+      <c r="O6" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="3"/>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C7" s="12">
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="2"/>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C7" s="4">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="14">
-        <v>100</v>
-      </c>
-      <c r="I7" s="3">
-        <v>100</v>
-      </c>
-      <c r="J7" s="3">
+      <c r="H7" s="10">
+        <v>50</v>
+      </c>
+      <c r="I7" s="2">
+        <v>50</v>
+      </c>
+      <c r="J7" s="2">
         <v>1800</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="2">
         <v>1800</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="2">
         <v>1800</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="2">
         <v>99</v>
       </c>
-      <c r="N7" s="20" t="s">
+      <c r="N7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="O7" s="20" t="s">
+      <c r="O7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14"/>
-      <c r="S7" s="3"/>
-    </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C8" s="12">
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C8" s="4">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="14">
-        <v>200</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="H8" s="10">
         <v>100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="I8" s="2">
+        <v>75</v>
+      </c>
+      <c r="J8" s="2">
         <v>1800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="2">
         <v>1800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="2">
         <v>1800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="2">
         <v>99</v>
       </c>
-      <c r="N8" s="20" t="s">
+      <c r="N8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="O8" s="20" t="s">
+      <c r="O8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
-      <c r="S8" s="3"/>
-    </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C9" s="12">
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C9" s="4">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="14">
-        <v>300</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="H9" s="10">
+        <v>150</v>
+      </c>
+      <c r="I9" s="2">
         <v>100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="2">
         <v>1800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="2">
         <v>1800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <v>1800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="2">
         <v>99</v>
       </c>
-      <c r="N9" s="22" t="s">
+      <c r="N9" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="O9" s="22" t="s">
+      <c r="O9" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="14"/>
-      <c r="S9" s="3"/>
-    </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
       <c r="N10" s="1"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="3"/>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
       <c r="N11" s="1"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="14"/>
-      <c r="R11" s="14"/>
-      <c r="S11" s="3"/>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="3"/>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="3"/>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="3"/>
-    </row>
-    <row r="15" s="3" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="14"/>
-    </row>
-    <row r="16" s="4" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="13"/>
-    </row>
-    <row r="17" s="4" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-    </row>
-    <row r="18" s="4" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="13"/>
-    </row>
-    <row r="19" s="4" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-    </row>
-    <row r="20" s="4" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
-    </row>
-    <row r="21" s="4" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="13"/>
-    </row>
-    <row r="22" s="4" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="P22" s="13"/>
-      <c r="Q22" s="13"/>
-      <c r="R22" s="13"/>
-    </row>
-    <row r="23" s="4" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13"/>
-      <c r="R23" s="13"/>
-    </row>
-    <row r="24" s="4" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="P24" s="13"/>
-      <c r="Q24" s="13"/>
-      <c r="R24" s="13"/>
-    </row>
-    <row r="25" s="3" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="14"/>
-      <c r="Q25" s="14"/>
-      <c r="R25" s="14"/>
-    </row>
-    <row r="26" s="3" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="14"/>
-      <c r="Q26" s="14"/>
-      <c r="R26" s="14"/>
-    </row>
-    <row r="27" s="3" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="14"/>
-      <c r="Q27" s="14"/>
-      <c r="R27" s="14"/>
-    </row>
-    <row r="28" s="3" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="14"/>
-      <c r="Q28" s="14"/>
-      <c r="R28" s="14"/>
-    </row>
-    <row r="29" s="3" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="14"/>
-      <c r="Q29" s="14"/>
-      <c r="R29" s="14"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="N3 O3 N4 O4 N5:O5 M3:M5 P3:R5 C3:L5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="N3:O3 N4:O4 N5:O5 C3:M5 P3:R5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterShengxiaoConfig.xlsx
+++ b/Excel/MonsterShengxiaoConfig.xlsx
@@ -86,13 +86,13 @@
     <t>天级·</t>
   </si>
   <si>
-    <t>200000</t>
+    <t>100000</t>
   </si>
   <si>
     <t>1000000000</t>
   </si>
   <si>
-    <t>10000000000</t>
+    <t>15000000000</t>
   </si>
   <si>
     <t>地级·</t>
@@ -104,7 +104,7 @@
     <t>3000000000</t>
   </si>
   <si>
-    <t>30000000000</t>
+    <t>50000000000</t>
   </si>
   <si>
     <t>玄级·</t>
@@ -116,7 +116,7 @@
     <t>9000000000</t>
   </si>
   <si>
-    <t>100000000000</t>
+    <t>150000000000</t>
   </si>
   <si>
     <t>黄级·</t>
@@ -128,7 +128,7 @@
     <t>20000000000</t>
   </si>
   <si>
-    <t>300000000000</t>
+    <t>500000000000</t>
   </si>
 </sst>
 </file>
@@ -773,7 +773,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -793,9 +793,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1165,9 +1162,9 @@
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
       <c r="S1" s="4"/>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -1185,9 +1182,9 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
       <c r="S2" s="4"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -1232,9 +1229,9 @@
       <c r="O3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
       <c r="S3" s="4"/>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -1279,9 +1276,9 @@
       <c r="O4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
       <c r="S4" s="4"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -1326,9 +1323,9 @@
       <c r="O5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
       <c r="S5" s="4"/>
     </row>
     <row r="6" customHeight="1" spans="3:19">
@@ -1338,13 +1335,13 @@
       <c r="D6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="14" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="10">
@@ -1365,10 +1362,10 @@
       <c r="M6" s="2">
         <v>99</v>
       </c>
-      <c r="N6" s="16" t="s">
+      <c r="N6" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="O6" s="16" t="s">
+      <c r="O6" s="15" t="s">
         <v>20</v>
       </c>
       <c r="P6" s="10"/>
@@ -1383,13 +1380,13 @@
       <c r="D7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="14" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="10">
@@ -1410,10 +1407,10 @@
       <c r="M7" s="2">
         <v>99</v>
       </c>
-      <c r="N7" s="16" t="s">
+      <c r="N7" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="O7" s="16" t="s">
+      <c r="O7" s="15" t="s">
         <v>24</v>
       </c>
       <c r="P7" s="10"/>
@@ -1427,13 +1424,13 @@
       <c r="D8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="14" t="s">
         <v>27</v>
       </c>
       <c r="H8" s="10">
@@ -1454,10 +1451,10 @@
       <c r="M8" s="2">
         <v>99</v>
       </c>
-      <c r="N8" s="16" t="s">
+      <c r="N8" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="O8" s="16" t="s">
+      <c r="O8" s="15" t="s">
         <v>28</v>
       </c>
       <c r="P8" s="10"/>
@@ -1471,13 +1468,13 @@
       <c r="D9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="14" t="s">
         <v>31</v>
       </c>
       <c r="H9" s="10">
@@ -1498,10 +1495,10 @@
       <c r="M9" s="2">
         <v>99</v>
       </c>
-      <c r="N9" s="17" t="s">
+      <c r="N9" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="O9" s="17" t="s">
+      <c r="O9" s="16" t="s">
         <v>32</v>
       </c>
       <c r="P9" s="10"/>
@@ -1511,7 +1508,7 @@
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:18">
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="11"/>
+      <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
@@ -1850,7 +1847,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="N3:O3 N4:O4 N5:O5 C3:M5 P3:R5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:R5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterShengxiaoConfig.xlsx
+++ b/Excel/MonsterShengxiaoConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="42">
   <si>
     <t>ID</t>
   </si>
@@ -86,49 +86,76 @@
     <t>天级·</t>
   </si>
   <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>800000000</t>
+  </si>
+  <si>
+    <t>15000000000</t>
+  </si>
+  <si>
+    <t>地级·</t>
+  </si>
+  <si>
+    <t>320000</t>
+  </si>
+  <si>
+    <t>2400000000</t>
+  </si>
+  <si>
+    <t>50000000000</t>
+  </si>
+  <si>
+    <t>玄级·</t>
+  </si>
+  <si>
+    <t>700000</t>
+  </si>
+  <si>
+    <t>7200000000</t>
+  </si>
+  <si>
+    <t>150000000000</t>
+  </si>
+  <si>
+    <t>黄级·</t>
+  </si>
+  <si>
+    <t>1600000</t>
+  </si>
+  <si>
+    <t>16000000000</t>
+  </si>
+  <si>
+    <t>500000000000</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
     <t>100000</t>
   </si>
   <si>
     <t>1000000000</t>
   </si>
   <si>
-    <t>15000000000</t>
-  </si>
-  <si>
-    <t>地级·</t>
-  </si>
-  <si>
     <t>400000</t>
   </si>
   <si>
     <t>3000000000</t>
   </si>
   <si>
-    <t>50000000000</t>
-  </si>
-  <si>
-    <t>玄级·</t>
-  </si>
-  <si>
     <t>800000</t>
   </si>
   <si>
     <t>9000000000</t>
   </si>
   <si>
-    <t>150000000000</t>
-  </si>
-  <si>
-    <t>黄级·</t>
-  </si>
-  <si>
     <t>2000000</t>
   </si>
   <si>
     <t>20000000000</t>
-  </si>
-  <si>
-    <t>500000000000</t>
   </si>
 </sst>
 </file>
@@ -1611,66 +1638,202 @@
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
     </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="10">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>25</v>
+      </c>
+      <c r="J16" s="2">
+        <v>100</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L16" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M16" s="2">
+        <v>99</v>
+      </c>
+      <c r="N16" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="O16" s="15" t="s">
+        <v>20</v>
+      </c>
       <c r="P16" s="10"/>
       <c r="Q16" s="10"/>
       <c r="R16" s="10"/>
     </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="4">
+        <v>2</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="10">
+        <v>50</v>
+      </c>
+      <c r="I17" s="2">
+        <v>50</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K17" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L17" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M17" s="2">
+        <v>99</v>
+      </c>
+      <c r="N17" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="O17" s="15" t="s">
+        <v>24</v>
+      </c>
       <c r="P17" s="10"/>
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
     </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="4">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" s="10">
+        <v>100</v>
+      </c>
+      <c r="I18" s="2">
+        <v>75</v>
+      </c>
+      <c r="J18" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L18" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M18" s="2">
+        <v>99</v>
+      </c>
+      <c r="N18" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="O18" s="15" t="s">
+        <v>28</v>
+      </c>
       <c r="P18" s="10"/>
       <c r="Q18" s="10"/>
       <c r="R18" s="10"/>
     </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="4">
+        <v>4</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="H19" s="10">
+        <v>150</v>
+      </c>
+      <c r="I19" s="2">
+        <v>100</v>
+      </c>
+      <c r="J19" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K19" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L19" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M19" s="2">
+        <v>99</v>
+      </c>
+      <c r="N19" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="O19" s="16" t="s">
+        <v>32</v>
+      </c>
       <c r="P19" s="10"/>
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>

--- a/Excel/MonsterShengxiaoConfig.xlsx
+++ b/Excel/MonsterShengxiaoConfig.xlsx
@@ -30,11 +30,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="49">
   <si>
     <t>ID</t>
   </si>
   <si>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t>Cycle</t>
+  </si>
+  <si>
     <t>MonsterName</t>
   </si>
   <si>
@@ -131,31 +137,46 @@
     <t>500000000000</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>1000000000</t>
-  </si>
-  <si>
-    <t>400000</t>
-  </si>
-  <si>
-    <t>3000000000</t>
-  </si>
-  <si>
-    <t>800000</t>
-  </si>
-  <si>
-    <t>9000000000</t>
+    <t>宇级·</t>
   </si>
   <si>
     <t>2000000</t>
   </si>
   <si>
-    <t>20000000000</t>
+    <t>40000000000</t>
+  </si>
+  <si>
+    <t>宙级·</t>
+  </si>
+  <si>
+    <t>6000000</t>
+  </si>
+  <si>
+    <t>160000000000</t>
+  </si>
+  <si>
+    <t>洪级·</t>
+  </si>
+  <si>
+    <t>20000000</t>
+  </si>
+  <si>
+    <t>600000000000</t>
+  </si>
+  <si>
+    <t>1500000000000</t>
+  </si>
+  <si>
+    <t>荒级·</t>
+  </si>
+  <si>
+    <t>60000000</t>
+  </si>
+  <si>
+    <t>2000000000000</t>
+  </si>
+  <si>
+    <t>5000000000000</t>
   </si>
 </sst>
 </file>
@@ -810,6 +831,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -819,12 +841,11 @@
     <xf numFmtId="176" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
@@ -1151,866 +1172,955 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S29"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
     <col min="2" max="2" width="8" style="3" customWidth="1"/>
-    <col min="3" max="3" width="9.875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="17" style="5" customWidth="1"/>
-    <col min="7" max="8" width="19.25" style="5" customWidth="1"/>
-    <col min="9" max="9" width="11.5" style="3" customWidth="1"/>
-    <col min="10" max="10" width="9.875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="10.375" style="3" customWidth="1"/>
-    <col min="12" max="12" width="12" style="3" customWidth="1"/>
-    <col min="13" max="13" width="9.375" style="3" customWidth="1"/>
-    <col min="14" max="14" width="15.25" style="3" customWidth="1"/>
-    <col min="15" max="15" width="17.0833333333333" style="3" customWidth="1"/>
-    <col min="16" max="16" width="11.625" style="5" customWidth="1"/>
-    <col min="17" max="17" width="17" style="5" customWidth="1"/>
-    <col min="18" max="18" width="19.25" style="5" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="3"/>
+    <col min="3" max="5" width="9.875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="16.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="17" style="5" customWidth="1"/>
+    <col min="9" max="9" width="19.25" style="5" customWidth="1"/>
+    <col min="10" max="10" width="15.75" style="5" customWidth="1"/>
+    <col min="11" max="11" width="11.5" style="3" customWidth="1"/>
+    <col min="12" max="12" width="9.875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="10.375" style="3" customWidth="1"/>
+    <col min="14" max="14" width="12" style="3" customWidth="1"/>
+    <col min="15" max="15" width="9.375" style="3" customWidth="1"/>
+    <col min="16" max="16" width="15.25" style="3" customWidth="1"/>
+    <col min="17" max="17" width="17.0833333333333" style="3" customWidth="1"/>
+    <col min="18" max="18" width="11.625" style="5" customWidth="1"/>
+    <col min="19" max="19" width="17" style="5" customWidth="1"/>
+    <col min="20" max="20" width="19.25" style="5" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:19">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="4"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="4"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="4"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="4"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="4"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="4"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
-      <c r="S3" s="4"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="P3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="R3" s="11"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="11"/>
+      <c r="U3" s="4"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
-      <c r="C4" s="7" t="s">
-        <v>13</v>
+      <c r="C4" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="M4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="N4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="O4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="4"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="P4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="4"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
-      <c r="C5" s="7" t="s">
-        <v>14</v>
+      <c r="C5" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="N5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="K5" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="4"/>
-    </row>
-    <row r="6" customHeight="1" spans="3:19">
+      <c r="L5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="4"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:21">
       <c r="C6" s="4">
         <v>1</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>18</v>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="10">
+        <v>20</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="12">
         <v>0</v>
       </c>
-      <c r="I6" s="2">
+      <c r="K6" s="2">
         <v>25</v>
       </c>
-      <c r="J6" s="2">
+      <c r="L6" s="2">
         <v>100</v>
       </c>
-      <c r="K6" s="2">
-        <v>1800</v>
-      </c>
-      <c r="L6" s="2">
-        <v>1800</v>
-      </c>
       <c r="M6" s="2">
+        <v>1800</v>
+      </c>
+      <c r="N6" s="2">
+        <v>1800</v>
+      </c>
+      <c r="O6" s="2">
         <v>99</v>
       </c>
-      <c r="N6" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="O6" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="2"/>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="P6" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q6" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="2"/>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:21">
       <c r="C7" s="4">
         <v>2</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>22</v>
+      <c r="D7" s="4">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="10">
+        <v>24</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="12">
         <v>50</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>50</v>
       </c>
-      <c r="J7" s="2">
-        <v>1800</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1800</v>
-      </c>
       <c r="L7" s="2">
         <v>1800</v>
       </c>
       <c r="M7" s="2">
+        <v>1800</v>
+      </c>
+      <c r="N7" s="2">
+        <v>1800</v>
+      </c>
+      <c r="O7" s="2">
         <v>99</v>
       </c>
-      <c r="N7" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="O7" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10"/>
-    </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="P7" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:21">
       <c r="C8" s="4">
         <v>3</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>26</v>
+      <c r="D8" s="4">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="10">
+        <v>28</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="12">
         <v>100</v>
       </c>
-      <c r="I8" s="2">
+      <c r="K8" s="2">
         <v>75</v>
       </c>
-      <c r="J8" s="2">
-        <v>1800</v>
-      </c>
-      <c r="K8" s="2">
-        <v>1800</v>
-      </c>
       <c r="L8" s="2">
         <v>1800</v>
       </c>
       <c r="M8" s="2">
+        <v>1800</v>
+      </c>
+      <c r="N8" s="2">
+        <v>1800</v>
+      </c>
+      <c r="O8" s="2">
         <v>99</v>
       </c>
-      <c r="N8" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="O8" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
-    </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="P8" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:21">
       <c r="C9" s="4">
         <v>4</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>30</v>
+      <c r="D9" s="4">
+        <v>4</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="10">
+        <v>32</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="12">
         <v>150</v>
       </c>
-      <c r="I9" s="2">
+      <c r="K9" s="2">
         <v>100</v>
       </c>
-      <c r="J9" s="2">
-        <v>1800</v>
-      </c>
-      <c r="K9" s="2">
-        <v>1800</v>
-      </c>
       <c r="L9" s="2">
         <v>1800</v>
       </c>
       <c r="M9" s="2">
+        <v>1800</v>
+      </c>
+      <c r="N9" s="2">
+        <v>1800</v>
+      </c>
+      <c r="O9" s="2">
         <v>99</v>
       </c>
-      <c r="N9" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="O9" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-    </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="P9" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q9" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:21">
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
-      <c r="N10" s="1"/>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="10"/>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:21">
+      <c r="C11" s="4">
+        <v>5</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" s="12">
+        <v>200</v>
+      </c>
+      <c r="K11" s="2">
+        <v>100</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M11" s="2">
+        <v>1800</v>
+      </c>
+      <c r="N11" s="2">
+        <v>1800</v>
+      </c>
+      <c r="O11" s="2">
+        <v>99</v>
+      </c>
+      <c r="P11" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q11" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="R11" s="12"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:21">
+      <c r="C12" s="4">
+        <v>6</v>
+      </c>
+      <c r="D12" s="4">
+        <v>2</v>
+      </c>
+      <c r="E12" s="4">
+        <v>2</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="J12" s="12">
+        <v>250</v>
+      </c>
+      <c r="K12" s="2">
+        <v>100</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M12" s="2">
+        <v>1800</v>
+      </c>
+      <c r="N12" s="2">
+        <v>1800</v>
+      </c>
+      <c r="O12" s="2">
+        <v>99</v>
+      </c>
+      <c r="P12" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q12" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:21">
+      <c r="C13" s="4">
+        <v>7</v>
+      </c>
+      <c r="D13" s="4">
+        <v>3</v>
+      </c>
+      <c r="E13" s="4">
+        <v>2</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13" s="12">
+        <v>300</v>
+      </c>
+      <c r="K13" s="2">
+        <v>100</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M13" s="2">
+        <v>1800</v>
+      </c>
+      <c r="N13" s="2">
+        <v>1800</v>
+      </c>
+      <c r="O13" s="2">
+        <v>99</v>
+      </c>
+      <c r="P13" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q13" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:21">
+      <c r="C14" s="4">
+        <v>8</v>
+      </c>
+      <c r="D14" s="4">
+        <v>4</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" s="12">
+        <v>350</v>
+      </c>
+      <c r="K14" s="2">
+        <v>100</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M14" s="2">
+        <v>1800</v>
+      </c>
+      <c r="N14" s="2">
+        <v>1800</v>
+      </c>
+      <c r="O14" s="2">
+        <v>99</v>
+      </c>
+      <c r="P14" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q14" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="12"/>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:21">
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="4">
-        <v>1</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16" s="10">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2">
-        <v>25</v>
-      </c>
-      <c r="J16" s="2">
-        <v>100</v>
-      </c>
-      <c r="K16" s="2">
-        <v>1800</v>
-      </c>
-      <c r="L16" s="2">
-        <v>1800</v>
-      </c>
-      <c r="M16" s="2">
-        <v>99</v>
-      </c>
-      <c r="N16" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="O16" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="10"/>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="4">
-        <v>2</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="H17" s="10">
-        <v>50</v>
-      </c>
-      <c r="I17" s="2">
-        <v>50</v>
-      </c>
-      <c r="J17" s="2">
-        <v>1800</v>
-      </c>
-      <c r="K17" s="2">
-        <v>1800</v>
-      </c>
-      <c r="L17" s="2">
-        <v>1800</v>
-      </c>
-      <c r="M17" s="2">
-        <v>99</v>
-      </c>
-      <c r="N17" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="O17" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="4">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="H18" s="10">
-        <v>100</v>
-      </c>
-      <c r="I18" s="2">
-        <v>75</v>
-      </c>
-      <c r="J18" s="2">
-        <v>1800</v>
-      </c>
-      <c r="K18" s="2">
-        <v>1800</v>
-      </c>
-      <c r="L18" s="2">
-        <v>1800</v>
-      </c>
-      <c r="M18" s="2">
-        <v>99</v>
-      </c>
-      <c r="N18" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="O18" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10"/>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="4">
-        <v>4</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="H19" s="10">
-        <v>150</v>
-      </c>
-      <c r="I19" s="2">
-        <v>100</v>
-      </c>
-      <c r="J19" s="2">
-        <v>1800</v>
-      </c>
-      <c r="K19" s="2">
-        <v>1800</v>
-      </c>
-      <c r="L19" s="2">
-        <v>1800</v>
-      </c>
-      <c r="M19" s="2">
-        <v>99</v>
-      </c>
-      <c r="N19" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="O19" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:21">
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="12"/>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:20">
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="R17" s="12"/>
+      <c r="S17" s="12"/>
+      <c r="T17" s="12"/>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="1:20">
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="1:20">
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="R19" s="12"/>
+      <c r="S19" s="12"/>
+      <c r="T19" s="12"/>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="1:20">
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="10"/>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="12"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12"/>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="1:20">
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="10"/>
-      <c r="R21" s="10"/>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="12"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="12"/>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="1:20">
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="10"/>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="12"/>
+      <c r="S22" s="12"/>
+      <c r="T22" s="12"/>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="1:20">
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
-      <c r="P23" s="10"/>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="10"/>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="12"/>
+      <c r="S23" s="12"/>
+      <c r="T23" s="12"/>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="1:20">
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="10"/>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="12"/>
+      <c r="S24" s="12"/>
+      <c r="T24" s="12"/>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="1:20">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="10"/>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="E25" s="4"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="12"/>
+      <c r="T25" s="12"/>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="1:20">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" s="10"/>
-      <c r="Q26" s="10"/>
-      <c r="R26" s="10"/>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="E26" s="4"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="5"/>
+      <c r="S26" s="12"/>
+      <c r="T26" s="12"/>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="1:20">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-      <c r="P27" s="10"/>
-      <c r="Q27" s="10"/>
-      <c r="R27" s="10"/>
-    </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="E27" s="4"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="12"/>
+      <c r="T27" s="12"/>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="1:20">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
-      <c r="P28" s="10"/>
-      <c r="Q28" s="10"/>
-      <c r="R28" s="10"/>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:18">
+      <c r="E28" s="4"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="12"/>
+      <c r="T28" s="12"/>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="1:20">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-      <c r="P29" s="10"/>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="10"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="5"/>
+      <c r="S29" s="12"/>
+      <c r="T29" s="12"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:R5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 D4 E4 D5 E5 C3:C5 F3:T5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterShengxiaoConfig.xlsx
+++ b/Excel/MonsterShengxiaoConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="53">
   <si>
     <t>ID</t>
   </si>
@@ -140,6 +140,9 @@
     <t>宇级·</t>
   </si>
   <si>
+    <t>1200000</t>
+  </si>
+  <si>
     <t>2000000</t>
   </si>
   <si>
@@ -149,6 +152,9 @@
     <t>宙级·</t>
   </si>
   <si>
+    <t>4000000</t>
+  </si>
+  <si>
     <t>6000000</t>
   </si>
   <si>
@@ -158,6 +164,9 @@
     <t>洪级·</t>
   </si>
   <si>
+    <t>12000000</t>
+  </si>
+  <si>
     <t>20000000</t>
   </si>
   <si>
@@ -168,6 +177,9 @@
   </si>
   <si>
     <t>荒级·</t>
+  </si>
+  <si>
+    <t>40000000</t>
   </si>
   <si>
     <t>60000000</t>
@@ -1635,10 +1647,10 @@
         <v>36</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J11" s="12">
         <v>200</v>
@@ -1679,16 +1691,16 @@
         <v>2</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J12" s="12">
         <v>250</v>
@@ -1729,16 +1741,16 @@
         <v>2</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J13" s="12">
         <v>300</v>
@@ -1759,10 +1771,10 @@
         <v>99</v>
       </c>
       <c r="P13" s="15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
@@ -1779,16 +1791,16 @@
         <v>2</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J14" s="12">
         <v>350</v>
@@ -1809,10 +1821,10 @@
         <v>99</v>
       </c>
       <c r="P14" s="16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="Q14" s="16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="R14" s="12"/>
       <c r="S14" s="12"/>
@@ -2120,7 +2132,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 D4 E4 D5 E5 C3:C5 F3:T5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:T5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterShengxiaoConfig.xlsx
+++ b/Excel/MonsterShengxiaoConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="62">
   <si>
     <t>ID</t>
   </si>
@@ -137,9 +137,6 @@
     <t>500000000000</t>
   </si>
   <si>
-    <t>宇级·</t>
-  </si>
-  <si>
     <t>1200000</t>
   </si>
   <si>
@@ -149,9 +146,6 @@
     <t>40000000000</t>
   </si>
   <si>
-    <t>宙级·</t>
-  </si>
-  <si>
     <t>4000000</t>
   </si>
   <si>
@@ -161,9 +155,6 @@
     <t>160000000000</t>
   </si>
   <si>
-    <t>洪级·</t>
-  </si>
-  <si>
     <t>12000000</t>
   </si>
   <si>
@@ -176,9 +167,6 @@
     <t>1500000000000</t>
   </si>
   <si>
-    <t>荒级·</t>
-  </si>
-  <si>
     <t>40000000</t>
   </si>
   <si>
@@ -189,6 +177,45 @@
   </si>
   <si>
     <t>5000000000000</t>
+  </si>
+  <si>
+    <t>5000000</t>
+  </si>
+  <si>
+    <t>10000000</t>
+  </si>
+  <si>
+    <t>200000000000</t>
+  </si>
+  <si>
+    <t>300000000000</t>
+  </si>
+  <si>
+    <t>30000000</t>
+  </si>
+  <si>
+    <t>800000000000</t>
+  </si>
+  <si>
+    <t>1000000000000</t>
+  </si>
+  <si>
+    <t>50000000</t>
+  </si>
+  <si>
+    <t>100000000</t>
+  </si>
+  <si>
+    <t>3000000000000</t>
+  </si>
+  <si>
+    <t>200000000</t>
+  </si>
+  <si>
+    <t>300000000</t>
+  </si>
+  <si>
+    <t>10000000000000</t>
   </si>
 </sst>
 </file>
@@ -833,7 +860,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -860,6 +887,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1424,13 +1454,13 @@
       <c r="F6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="15" t="s">
         <v>21</v>
       </c>
       <c r="J6" s="12">
@@ -1451,10 +1481,10 @@
       <c r="O6" s="2">
         <v>99</v>
       </c>
-      <c r="P6" s="15" t="s">
+      <c r="P6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="Q6" s="15" t="s">
+      <c r="Q6" s="16" t="s">
         <v>22</v>
       </c>
       <c r="R6" s="12"/>
@@ -1475,13 +1505,13 @@
       <c r="F7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="15" t="s">
         <v>25</v>
       </c>
       <c r="J7" s="12">
@@ -1502,10 +1532,10 @@
       <c r="O7" s="2">
         <v>99</v>
       </c>
-      <c r="P7" s="15" t="s">
+      <c r="P7" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="Q7" s="15" t="s">
+      <c r="Q7" s="16" t="s">
         <v>26</v>
       </c>
       <c r="R7" s="12"/>
@@ -1525,13 +1555,13 @@
       <c r="F8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="15" t="s">
         <v>29</v>
       </c>
       <c r="J8" s="12">
@@ -1552,10 +1582,10 @@
       <c r="O8" s="2">
         <v>99</v>
       </c>
-      <c r="P8" s="15" t="s">
+      <c r="P8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="Q8" s="15" t="s">
+      <c r="Q8" s="16" t="s">
         <v>30</v>
       </c>
       <c r="R8" s="12"/>
@@ -1575,13 +1605,13 @@
       <c r="F9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="15" t="s">
         <v>33</v>
       </c>
       <c r="J9" s="12">
@@ -1602,10 +1632,10 @@
       <c r="O9" s="2">
         <v>99</v>
       </c>
-      <c r="P9" s="16" t="s">
+      <c r="P9" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="Q9" s="16" t="s">
+      <c r="Q9" s="17" t="s">
         <v>34</v>
       </c>
       <c r="R9" s="12"/>
@@ -1641,16 +1671,16 @@
         <v>2</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="H11" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="I11" s="15" t="s">
         <v>37</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>38</v>
       </c>
       <c r="J11" s="12">
         <v>200</v>
@@ -1670,10 +1700,10 @@
       <c r="O11" s="2">
         <v>99</v>
       </c>
-      <c r="P11" s="15" t="s">
+      <c r="P11" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="Q11" s="15" t="s">
+      <c r="Q11" s="16" t="s">
         <v>30</v>
       </c>
       <c r="R11" s="12"/>
@@ -1691,16 +1721,16 @@
         <v>2</v>
       </c>
       <c r="F12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="I12" s="15" t="s">
         <v>40</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="I12" s="14" t="s">
-        <v>42</v>
       </c>
       <c r="J12" s="12">
         <v>250</v>
@@ -1720,10 +1750,10 @@
       <c r="O12" s="2">
         <v>99</v>
       </c>
-      <c r="P12" s="15" t="s">
+      <c r="P12" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="Q12" s="15" t="s">
+      <c r="Q12" s="16" t="s">
         <v>34</v>
       </c>
       <c r="R12" s="12"/>
@@ -1741,16 +1771,16 @@
         <v>2</v>
       </c>
       <c r="F13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" s="15" t="s">
         <v>43</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>46</v>
       </c>
       <c r="J13" s="12">
         <v>300</v>
@@ -1770,11 +1800,11 @@
       <c r="O13" s="2">
         <v>99</v>
       </c>
-      <c r="P13" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q13" s="15" t="s">
-        <v>47</v>
+      <c r="P13" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q13" s="16" t="s">
+        <v>44</v>
       </c>
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
@@ -1791,16 +1821,16 @@
         <v>2</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I14" s="14" t="s">
-        <v>51</v>
+        <v>31</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>47</v>
       </c>
       <c r="J14" s="12">
         <v>350</v>
@@ -1820,11 +1850,11 @@
       <c r="O14" s="2">
         <v>99</v>
       </c>
-      <c r="P14" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q14" s="16" t="s">
-        <v>52</v>
+      <c r="P14" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q14" s="17" t="s">
+        <v>48</v>
       </c>
       <c r="R14" s="12"/>
       <c r="S14" s="12"/>
@@ -1849,73 +1879,201 @@
       <c r="T15" s="12"/>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="1:21">
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+      <c r="C16" s="4">
+        <v>9</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>3</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="J16" s="12">
+        <v>250</v>
+      </c>
+      <c r="K16" s="2">
+        <v>100</v>
+      </c>
+      <c r="L16" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M16" s="2">
+        <v>1800</v>
+      </c>
+      <c r="N16" s="2">
+        <v>1800</v>
+      </c>
+      <c r="O16" s="2">
+        <v>99</v>
+      </c>
+      <c r="P16" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q16" s="16" t="s">
+        <v>52</v>
+      </c>
       <c r="R16" s="12"/>
       <c r="S16" s="12"/>
       <c r="T16" s="12"/>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="1:20">
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+      <c r="C17" s="4">
+        <v>10</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2</v>
+      </c>
+      <c r="E17" s="4">
+        <v>3</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="J17" s="12">
+        <v>300</v>
+      </c>
+      <c r="K17" s="2">
+        <v>100</v>
+      </c>
+      <c r="L17" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M17" s="2">
+        <v>1800</v>
+      </c>
+      <c r="N17" s="2">
+        <v>1800</v>
+      </c>
+      <c r="O17" s="2">
+        <v>99</v>
+      </c>
+      <c r="P17" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q17" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="R17" s="12"/>
       <c r="S17" s="12"/>
       <c r="T17" s="12"/>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="1:20">
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+      <c r="C18" s="4">
+        <v>11</v>
+      </c>
+      <c r="D18" s="4">
+        <v>3</v>
+      </c>
+      <c r="E18" s="4">
+        <v>3</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="J18" s="12">
+        <v>350</v>
+      </c>
+      <c r="K18" s="2">
+        <v>100</v>
+      </c>
+      <c r="L18" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M18" s="2">
+        <v>1800</v>
+      </c>
+      <c r="N18" s="2">
+        <v>1800</v>
+      </c>
+      <c r="O18" s="2">
+        <v>99</v>
+      </c>
+      <c r="P18" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q18" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="R18" s="12"/>
       <c r="S18" s="12"/>
       <c r="T18" s="12"/>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="1:20">
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+      <c r="C19" s="4">
+        <v>12</v>
+      </c>
+      <c r="D19" s="4">
+        <v>4</v>
+      </c>
+      <c r="E19" s="4">
+        <v>3</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="J19" s="12">
+        <v>400</v>
+      </c>
+      <c r="K19" s="2">
+        <v>100</v>
+      </c>
+      <c r="L19" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M19" s="2">
+        <v>1800</v>
+      </c>
+      <c r="N19" s="2">
+        <v>1800</v>
+      </c>
+      <c r="O19" s="2">
+        <v>99</v>
+      </c>
+      <c r="P19" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q19" s="17" t="s">
+        <v>61</v>
+      </c>
       <c r="R19" s="12"/>
       <c r="S19" s="12"/>
       <c r="T19" s="12"/>
@@ -1925,9 +2083,9 @@
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
       <c r="J20" s="12"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>

--- a/Excel/MonsterShengxiaoConfig.xlsx
+++ b/Excel/MonsterShengxiaoConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="64">
   <si>
     <t>ID</t>
   </si>
@@ -179,40 +179,46 @@
     <t>5000000000000</t>
   </si>
   <si>
-    <t>5000000</t>
-  </si>
-  <si>
     <t>10000000</t>
   </si>
   <si>
-    <t>200000000000</t>
+    <t>240000000000</t>
   </si>
   <si>
     <t>300000000000</t>
   </si>
   <si>
+    <t>24000000</t>
+  </si>
+  <si>
     <t>30000000</t>
   </si>
   <si>
-    <t>800000000000</t>
+    <t>960000000000</t>
   </si>
   <si>
     <t>1000000000000</t>
   </si>
   <si>
-    <t>50000000</t>
+    <t>72000000</t>
   </si>
   <si>
     <t>100000000</t>
   </si>
   <si>
+    <t>3600000000000</t>
+  </si>
+  <si>
     <t>3000000000000</t>
   </si>
   <si>
-    <t>200000000</t>
+    <t>240000000</t>
   </si>
   <si>
     <t>300000000</t>
+  </si>
+  <si>
+    <t>12000000000000</t>
   </si>
   <si>
     <t>10000000000000</t>
@@ -1892,13 +1898,13 @@
         <v>19</v>
       </c>
       <c r="G16" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="I16" s="15" t="s">
         <v>50</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>51</v>
       </c>
       <c r="J16" s="12">
         <v>250</v>
@@ -1919,10 +1925,10 @@
         <v>99</v>
       </c>
       <c r="P16" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q16" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R16" s="12"/>
       <c r="S16" s="12"/>
@@ -1942,7 +1948,7 @@
         <v>23</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="H17" s="15" t="s">
         <v>53</v>
@@ -2019,10 +2025,10 @@
         <v>99</v>
       </c>
       <c r="P18" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q18" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R18" s="12"/>
       <c r="S18" s="12"/>
@@ -2042,13 +2048,13 @@
         <v>31</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J19" s="12">
         <v>400</v>
@@ -2069,10 +2075,10 @@
         <v>99</v>
       </c>
       <c r="P19" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Q19" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="R19" s="12"/>
       <c r="S19" s="12"/>
